--- a/experiments/04_lora_finetuning/report/base_few_shots_vs_lora_1_epoch.xlsx
+++ b/experiments/04_lora_finetuning/report/base_few_shots_vs_lora_1_epoch.xlsx
@@ -542,18 +542,18 @@
   <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
